--- a/artfynd/S 914-2026 artfynd.xlsx
+++ b/artfynd/S 914-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -969,6 +969,111 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135468918</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Barrskog, Brattås, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>814153</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7162306</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Staffan Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Staffan Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 914-2026 artfynd.xlsx
+++ b/artfynd/S 914-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/304698</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1672595</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1830953</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1073,8 +1093,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135468918</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 914-2026 artfynd.xlsx
+++ b/artfynd/S 914-2026 artfynd.xlsx
@@ -994,7 +994,7 @@
         <v>135468918</v>
       </c>
       <c r="B5" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 914-2026 artfynd.xlsx
+++ b/artfynd/S 914-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -986,6 +986,116 @@
       <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/1830953</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135468918</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Barrskog, Brattås, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>814153</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7162306</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Staffan Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Staffan Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135468918</t>
         </is>
       </c>
     </row>
@@ -994,6 +1104,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 914-2026 artfynd.xlsx
+++ b/artfynd/S 914-2026 artfynd.xlsx
@@ -994,7 +994,7 @@
         <v>135468918</v>
       </c>
       <c r="B5" t="n">
-        <v>58136</v>
+        <v>58138</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
